--- a/groups.xlsx
+++ b/groups.xlsx
@@ -2598,8 +2598,9 @@
       <x:c r="A77" s="2" t="str">
         <x:v>AST5_AIS5_S1</x:v>
       </x:c>
-      <x:c r="B77" s="4" t="str">
-        <x:v>Abdelrahman Ahmed Elsayed Ahmed	alhaishabdo@gmail.com
+      <x:c r="B77" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abdelrahman Ahmed Elsayed Ahmed	alhaishabdo@gmail.com
 Ali Mohamed Eid Ahmed	alimohamedeid.sy@gmail.com
 amany mustafa omran aboelez	mustafaamany704@gmail.com
 Bahgat Zakaria Bahgat Marcos	bahgatzakaria653@gmail.com
@@ -2622,7 +2623,10 @@
 rawan shreif mohamed youssef	elhalwanyrawan14@gmail.com
 rawda shreif mohamed youssef	rawdashrei8@gmail.com
 Sara Yasser Ahmed Abd Elhamed	sarayaseer668@gmail.com
-Youssef Mohamed Mahmoud Elfarouk Abdelrazek	s-youssef.abdelrazek@zewailcity.edu.eg</x:v>
+Youssef Mohamed Mahmoud Elfarouk Abdelrazek	s-youssef.abdelrazek@zewailcity.edu.eg
+Haneen Mohamed Hamza Abdelwahed	haneenmohamed22ixi@gmail.com
+Ahmed Amr Farag Kotb	ahmed214372@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="78" ht="224" customHeight="1">
@@ -2865,8 +2869,9 @@
       <x:c r="A86" s="2" t="str">
         <x:v>CAI5_SWD5_S2</x:v>
       </x:c>
-      <x:c r="B86" s="4" t="str">
-        <x:v>Abdelrahman Ahmed Abdelrazek Ali	abdelrhman8545@gmail.com
+      <x:c r="B86" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abdelrahman Ahmed Abdelrazek Ali	abdelrhman8545@gmail.com
 Abdulrahaman Ahmed Abdelraheem Abozeid	ba7243277@gmail.com
 Ahmed Mohammed Hanfey Issa	ahmed.mhanfey@gmail.com
 Ahmed Said Dorgham Eisaa	ahmedsaid1972.9@gmail.com
@@ -2890,15 +2895,18 @@
 Toka Ahmed Ragab Kenawy	totak82005@gmail.com
 Yasmin Emad Eldin Mohamed Atia	yasminemadaldeen729@gmail.com
 Yousif Ahmed Hassan Nouraldien	josefahmed357@gmail.com
-youssef ahmed mohamed alwasify	yousefalwasefy@gmail.com</x:v>
+youssef ahmed mohamed alwasify	yousefalwasefy@gmail.com
+Huda Abdullah Ahmad	hoda.abdallah2006@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="87" ht="240" customHeight="1">
       <x:c r="A87" s="2" t="str">
         <x:v>CAI5_SWD5_S3</x:v>
       </x:c>
-      <x:c r="B87" s="4" t="str">
-        <x:v>Abanoub Malak Aziz Mansour	abanoubmalak886@gmail.com
+      <x:c r="B87" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abanoub Malak Aziz Mansour	abanoubmalak886@gmail.com
 Abdelrahman Eslam Ahmed Wajih Abdulmajeed	abdelrahman555rrr@gmail.com
 Adham Ashraf Ali Higazy	adhamashrafali@gmail.com
 ahmed qobasy lotfy ahmed	qebasyahmed@gmail.com
@@ -2921,7 +2929,9 @@
 noor nader mahmoud ellithy	noor.nader.bis24@fcba.capu.edu.eg
 ola sherif abdel mohsen zaki	olasherif459@gmail.com
 Tameer Saeed Ahmed Alwakel	timotameer123@gmail.com
-Youssef Diaa Abdelrahman Gabr	youssefdiaa19@gmail.com</x:v>
+Youssef Diaa Abdelrahman Gabr	youssefdiaa19@gmail.com
+mokhtar mostafa mokhtar mostafa	mukhtarmustafa22@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="88" ht="240" customHeight="1">
@@ -3411,8 +3421,9 @@
       <x:c r="A103" s="2" t="str">
         <x:v>ONL5_ISS3_S4</x:v>
       </x:c>
-      <x:c r="B103" s="4" t="str">
-        <x:v>Abanoub Ebid Thapt Daoud	2400453@student.eelu.edu.eg
+      <x:c r="B103" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abanoub Ebid Thapt Daoud	2400453@student.eelu.edu.eg
 Abdallah Ahmed Abdelrashid Abdelbaqy	2401641@student.eelu.edu.eg
 Abdelaziz Mohamed Abdelaziz Ali	2302243@student.eelu.edu.eg
 Abdelrahman Ahmed Saad Hashem	1abdelrahman.saad1@gmail.com
@@ -3439,15 +3450,19 @@
 Sayed Ahmed Mohamed Sayed	sayedagag926@gmail.com
 sohir Eed Douksh Ayad	sohireldouksh@gmail.com
 Walid Mazher Hanfi Abu Zaid	walidmazher6@gmail.com
-Zolfa Mohamed Mahmoud Mohamed	zolfafarghaly@gmail.com</x:v>
+Zolfa Mohamed Mahmoud Mohamed	zolfafarghaly@gmail.com
+Malak Mohamed Ali Awadallah	malakmohamedalii2005@gmail.com
+Ola Ayman Shoukry Abdelsalam	olaayman586@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="104" ht="240" customHeight="1">
       <x:c r="A104" s="2" t="str">
         <x:v>ONL5_SWD5_G1</x:v>
       </x:c>
-      <x:c r="B104" s="4" t="str">
-        <x:v>Abanub Awad Adel Awad	abanub.awad.dev@gmail.com
+      <x:c r="B104" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abanub Awad Adel Awad	abanub.awad.dev@gmail.com
 Abdullh Elrefay Hamed Shehata	abdullhshehata10@gmail.com
 Ahmed Gamal Khairy Hassan	ahmedgamalkhairy842001@gmail.com
 Ahmed Hassan Ali Abotayesh	aabwtaysh@gmail.com
@@ -3475,7 +3490,9 @@
 Omnia Islam Salah Mohamed	omniaislam534@gmail.com
 Ramy Wageh Zaki AbdElmalak	ramywageh1996@gmail.com
 Rawan Abdo Abdo Sheta	rsheta42@gmail.com
-waleed ahmed korashy abdo	wqorashy@gmail.com</x:v>
+waleed ahmed korashy abdo	wqorashy@gmail.com
+Essam Makram Malak Salib	essam.makram.549@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="105" ht="210" customHeight="1">
@@ -3698,8 +3715,9 @@
       <x:c r="A113" s="2" t="str">
         <x:v>QAL5_SWD6_S1</x:v>
       </x:c>
-      <x:c r="B113" s="4" t="str">
-        <x:v>Abdelhamid Adel Abdelhamid Abdelrahman	abdelhamida939@gmail.com
+      <x:c r="B113" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Abdelhamid Adel Abdelhamid Abdelrahman	abdelhamida939@gmail.com
 Ahmed Mostafa Metwaly Fadelallh	ahmemostafa900@gmail.com
 ahmed rabeaa abdelmoneim abdelrahman	ahmedrabeaa539@gmail.com
 ALMOATAZ BILLAH EMAD SOLIMAN	moatazemad382@gmail.com
@@ -3712,7 +3730,9 @@
 sara morsy abbas saqr	sarasakr852@gmail.com
 Serag eldin Ashraf Elsayed Ahmed	siragashraf001@gmail.com
 Shrouk Maher Abdo Meslhy	shrokmaher498@gmail.com
-Hesham Ibrahim El Sebaey Mohammed	chevalier.sans.monture1@gmail.com</x:v>
+Hesham Ibrahim El Sebaey Mohammed	chevalier.sans.monture1@gmail.com
+Omar Mohamed Atwa Ahmed	oatwa284@gmail.com</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
